--- a/Calendario_Campionato.xlsx
+++ b/Calendario_Campionato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>Calendario Campionato</t>
   </si>
@@ -188,151 +188,178 @@
     <t>1-4</t>
   </si>
   <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>13ª Giornata lega</t>
+  </si>
+  <si>
+    <t>15ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>14ª Giornata lega</t>
+  </si>
+  <si>
+    <t>16ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>15ª Giornata lega</t>
+  </si>
+  <si>
+    <t>17ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>16ª Giornata lega</t>
+  </si>
+  <si>
+    <t>18ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>5-3</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>17ª Giornata lega</t>
+  </si>
+  <si>
+    <t>19ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>18ª Giornata lega</t>
+  </si>
+  <si>
+    <t>20ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>4-4</t>
+  </si>
+  <si>
+    <t>19ª Giornata lega</t>
+  </si>
+  <si>
+    <t>21ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>20ª Giornata lega</t>
+  </si>
+  <si>
+    <t>22ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>21ª Giornata lega</t>
+  </si>
+  <si>
+    <t>23ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>22ª Giornata lega</t>
+  </si>
+  <si>
+    <t>24ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>6-2</t>
+  </si>
+  <si>
+    <t>23ª Giornata lega</t>
+  </si>
+  <si>
+    <t>25ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>24ª Giornata lega</t>
+  </si>
+  <si>
+    <t>26ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>25ª Giornata lega</t>
+  </si>
+  <si>
+    <t>27ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>26ª Giornata lega</t>
+  </si>
+  <si>
+    <t>28ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>27ª Giornata lega</t>
+  </si>
+  <si>
+    <t>29ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>28ª Giornata lega</t>
+  </si>
+  <si>
+    <t>30ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>29ª Giornata lega</t>
+  </si>
+  <si>
+    <t>31ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>30ª Giornata lega</t>
+  </si>
+  <si>
+    <t>32ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>31ª Giornata lega</t>
+  </si>
+  <si>
+    <t>33ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>32ª Giornata lega</t>
+  </si>
+  <si>
+    <t>34ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>33ª Giornata lega</t>
+  </si>
+  <si>
+    <t>35ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>34ª Giornata lega</t>
+  </si>
+  <si>
+    <t>36ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>35ª Giornata lega</t>
+  </si>
+  <si>
+    <t>37ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>36ª Giornata lega</t>
+  </si>
+  <si>
+    <t>38ª Giornata serie a</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>13ª Giornata lega</t>
-  </si>
-  <si>
-    <t>15ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>14ª Giornata lega</t>
-  </si>
-  <si>
-    <t>16ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>15ª Giornata lega</t>
-  </si>
-  <si>
-    <t>17ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>16ª Giornata lega</t>
-  </si>
-  <si>
-    <t>18ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>17ª Giornata lega</t>
-  </si>
-  <si>
-    <t>19ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>18ª Giornata lega</t>
-  </si>
-  <si>
-    <t>20ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>19ª Giornata lega</t>
-  </si>
-  <si>
-    <t>21ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>20ª Giornata lega</t>
-  </si>
-  <si>
-    <t>22ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>21ª Giornata lega</t>
-  </si>
-  <si>
-    <t>23ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>22ª Giornata lega</t>
-  </si>
-  <si>
-    <t>24ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>23ª Giornata lega</t>
-  </si>
-  <si>
-    <t>25ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>24ª Giornata lega</t>
-  </si>
-  <si>
-    <t>26ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>25ª Giornata lega</t>
-  </si>
-  <si>
-    <t>27ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>26ª Giornata lega</t>
-  </si>
-  <si>
-    <t>28ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>27ª Giornata lega</t>
-  </si>
-  <si>
-    <t>29ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>28ª Giornata lega</t>
-  </si>
-  <si>
-    <t>30ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>29ª Giornata lega</t>
-  </si>
-  <si>
-    <t>31ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>30ª Giornata lega</t>
-  </si>
-  <si>
-    <t>32ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>31ª Giornata lega</t>
-  </si>
-  <si>
-    <t>33ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>32ª Giornata lega</t>
-  </si>
-  <si>
-    <t>34ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>33ª Giornata lega</t>
-  </si>
-  <si>
-    <t>35ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>34ª Giornata lega</t>
-  </si>
-  <si>
-    <t>36ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>35ª Giornata lega</t>
-  </si>
-  <si>
-    <t>37ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>36ª Giornata lega</t>
-  </si>
-  <si>
-    <t>38ª Giornata serie a</t>
   </si>
 </sst>
 </file>
@@ -1267,16 +1294,16 @@
         <v>6</v>
       </c>
       <c r="H30" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="I30" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1299,16 +1326,16 @@
         <v>9</v>
       </c>
       <c r="H31" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="I31" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1331,10 +1358,10 @@
         <v>12</v>
       </c>
       <c r="H32" s="6">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I32" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>14</v>
@@ -1363,16 +1390,16 @@
         <v>7</v>
       </c>
       <c r="H33" s="6">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I33" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -1400,31 +1427,31 @@
         <v>17</v>
       </c>
       <c r="B35" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="C35" s="6">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="I35" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1432,31 +1459,31 @@
         <v>14</v>
       </c>
       <c r="B36" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="C36" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H36" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I36" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -1464,31 +1491,31 @@
         <v>12</v>
       </c>
       <c r="B37" s="6">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="C37" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H37" s="6">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I37" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1496,31 +1523,31 @@
         <v>11</v>
       </c>
       <c r="B38" s="6">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="C38" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H38" s="6">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I38" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>12</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -1548,31 +1575,31 @@
         <v>6</v>
       </c>
       <c r="B40" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="C40" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H40" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I40" s="6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
@@ -1580,31 +1607,31 @@
         <v>11</v>
       </c>
       <c r="B41" s="6">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C41" s="6">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="I41" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1612,31 +1639,31 @@
         <v>15</v>
       </c>
       <c r="B42" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C42" s="6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H42" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="I42" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1644,49 +1671,49 @@
         <v>9</v>
       </c>
       <c r="B43" s="6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="C43" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H43" s="6">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I43" s="6">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>6</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
       <c r="G44" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="4"/>
@@ -1696,31 +1723,31 @@
         <v>11</v>
       </c>
       <c r="B45" s="6">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C45" s="6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H45" s="6">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="I45" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46">
@@ -1728,31 +1755,31 @@
         <v>15</v>
       </c>
       <c r="B46" s="6">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="C46" s="6">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H46" s="6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I46" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1760,31 +1787,31 @@
         <v>9</v>
       </c>
       <c r="B47" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C47" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H47" s="6">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="I47" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -1792,49 +1819,49 @@
         <v>17</v>
       </c>
       <c r="B48" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="C48" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I48" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="4"/>
       <c r="G49" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="4"/>
@@ -1844,31 +1871,31 @@
         <v>11</v>
       </c>
       <c r="B50" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C50" s="6">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H50" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="I50" s="6">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="J50" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51">
@@ -1876,31 +1903,31 @@
         <v>15</v>
       </c>
       <c r="B51" s="6">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C51" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H51" s="6">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I51" s="6">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="J51" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
@@ -1908,31 +1935,31 @@
         <v>14</v>
       </c>
       <c r="B52" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C52" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I52" s="6">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
@@ -1940,49 +1967,49 @@
         <v>17</v>
       </c>
       <c r="B53" s="6">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="C53" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H53" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I53" s="6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
       <c r="G54" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="4"/>
@@ -1992,31 +2019,31 @@
         <v>11</v>
       </c>
       <c r="B55" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C55" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H55" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="I55" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="J55" s="7" t="s">
         <v>6</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -2024,31 +2051,31 @@
         <v>14</v>
       </c>
       <c r="B56" s="6">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="C56" s="6">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H56" s="6">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I56" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57">
@@ -2056,31 +2083,31 @@
         <v>17</v>
       </c>
       <c r="B57" s="6">
-        <v>0</v>
+        <v>81.5</v>
       </c>
       <c r="C57" s="6">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H57" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I57" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J57" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
@@ -2088,49 +2115,49 @@
         <v>12</v>
       </c>
       <c r="B58" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="C58" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="6">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I58" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="J58" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
       <c r="G59" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="4"/>
@@ -2140,31 +2167,31 @@
         <v>9</v>
       </c>
       <c r="B60" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="C60" s="6">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="6">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="I60" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="J60" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
@@ -2172,31 +2199,31 @@
         <v>15</v>
       </c>
       <c r="B61" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C61" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H61" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="I61" s="6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -2204,31 +2231,31 @@
         <v>11</v>
       </c>
       <c r="B62" s="6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C62" s="6">
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H62" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I62" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="J62" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -2236,49 +2263,49 @@
         <v>6</v>
       </c>
       <c r="B63" s="6">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="C63" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H63" s="6">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="I63" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J63" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="4"/>
       <c r="G64" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="4"/>
@@ -2288,31 +2315,31 @@
         <v>15</v>
       </c>
       <c r="B65" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C65" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H65" s="6">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="I65" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="J65" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -2320,31 +2347,31 @@
         <v>11</v>
       </c>
       <c r="B66" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C66" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H66" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I66" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="J66" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -2352,31 +2379,31 @@
         <v>17</v>
       </c>
       <c r="B67" s="6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C67" s="6">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H67" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I67" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J67" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68">
@@ -2384,49 +2411,49 @@
         <v>9</v>
       </c>
       <c r="B68" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C68" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H68" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="I68" s="6">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="J68" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
       <c r="G69" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="4"/>
@@ -2436,31 +2463,31 @@
         <v>17</v>
       </c>
       <c r="B70" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="C70" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H70" s="6">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I70" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
@@ -2468,31 +2495,31 @@
         <v>14</v>
       </c>
       <c r="B71" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C71" s="6">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H71" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="I71" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="J71" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2500,31 +2527,31 @@
         <v>12</v>
       </c>
       <c r="B72" s="6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="C72" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H72" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="I72" s="6">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="J72" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73">
@@ -2532,49 +2559,49 @@
         <v>11</v>
       </c>
       <c r="B73" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C73" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H73" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="I73" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>12</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="4"/>
@@ -2584,31 +2611,31 @@
         <v>6</v>
       </c>
       <c r="B75" s="6">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="C75" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H75" s="6">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="I75" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J75" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
@@ -2616,31 +2643,31 @@
         <v>11</v>
       </c>
       <c r="B76" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="C76" s="6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H76" s="6">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="I76" s="6">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J76" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
@@ -2648,31 +2675,31 @@
         <v>15</v>
       </c>
       <c r="B77" s="6">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C77" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H77" s="6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I77" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78">
@@ -2680,49 +2707,49 @@
         <v>9</v>
       </c>
       <c r="B78" s="6">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="C78" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H78" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I78" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="J78" s="7" t="s">
         <v>6</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="4"/>
       <c r="G79" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="4"/>
@@ -2732,31 +2759,31 @@
         <v>11</v>
       </c>
       <c r="B80" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C80" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H80" s="6">
-        <v>0</v>
+        <v>81.5</v>
       </c>
       <c r="I80" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
@@ -2764,31 +2791,31 @@
         <v>15</v>
       </c>
       <c r="B81" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C81" s="6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H81" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I81" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82">
@@ -2796,31 +2823,31 @@
         <v>9</v>
       </c>
       <c r="B82" s="6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C82" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H82" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="I82" s="6">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="J82" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -2828,49 +2855,49 @@
         <v>17</v>
       </c>
       <c r="B83" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C83" s="6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H83" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="I83" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J83" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
       <c r="G84" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="4"/>
@@ -2880,31 +2907,31 @@
         <v>11</v>
       </c>
       <c r="B85" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="C85" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H85" s="6">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I85" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86">
@@ -2912,31 +2939,31 @@
         <v>15</v>
       </c>
       <c r="B86" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="C86" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H86" s="6">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I86" s="6">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J86" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87">
@@ -2944,31 +2971,31 @@
         <v>14</v>
       </c>
       <c r="B87" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="C87" s="6">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H87" s="6">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="I87" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J87" s="7" t="s">
         <v>12</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88">
@@ -2976,49 +3003,49 @@
         <v>17</v>
       </c>
       <c r="B88" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="C88" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H88" s="6">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="I88" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="J88" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
       <c r="G89" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J89" s="3"/>
       <c r="K89" s="4"/>
@@ -3028,16 +3055,16 @@
         <v>11</v>
       </c>
       <c r="B90" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="C90" s="6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>7</v>
@@ -3052,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91">
@@ -3060,16 +3087,16 @@
         <v>14</v>
       </c>
       <c r="B91" s="6">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="C91" s="6">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>12</v>
@@ -3084,7 +3111,7 @@
         <v>11</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92">
@@ -3092,16 +3119,16 @@
         <v>17</v>
       </c>
       <c r="B92" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C92" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>17</v>
@@ -3116,7 +3143,7 @@
         <v>15</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93">
@@ -3124,16 +3151,16 @@
         <v>12</v>
       </c>
       <c r="B93" s="6">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="C93" s="6">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>14</v>
@@ -3148,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
